--- a/VerveStacks_CHN_grids_kan60/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_CHN_grids_kan60/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B988A81B-DA16-4B0C-B696-BAA6C77E86E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A5F553D-60E6-4A33-BDAA-F86D8305B6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="12772" activeTab="1" xr2:uid="{8219D838-14BC-4F44-9947-F7BFB828DBAC}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{7E2EA236-5D15-4476-B2D5-65A960953883}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3837,7 +3837,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8761A944-AC55-4CFF-80FA-C0C031ED6007}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64846C3C-272D-4088-A8E7-6F1135B96DF7}">
   <dimension ref="B3:S346"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12806,7 +12806,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{707EE260-1DCF-40FF-B312-77E7AA08357E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB4B9FE8-2649-43D0-B11F-1C913FA6B827}">
   <dimension ref="B3:L85"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHN_grids_kan60/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_CHN_grids_kan60/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A5F553D-60E6-4A33-BDAA-F86D8305B6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E6B17DF-E45F-4922-B729-23B2F5C01534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{7E2EA236-5D15-4476-B2D5-65A960953883}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{2A19D64C-E665-4C5D-A1E9-A47E73BD3DB6}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3837,7 +3837,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64846C3C-272D-4088-A8E7-6F1135B96DF7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D444407B-AEB7-4F20-AF58-B41552785B9E}">
   <dimension ref="B3:S346"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12806,7 +12806,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB4B9FE8-2649-43D0-B11F-1C913FA6B827}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5370EE85-A169-4E28-9D64-DFFDD015BA1E}">
   <dimension ref="B3:L85"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHN_grids_kan60/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_CHN_grids_kan60/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E6B17DF-E45F-4922-B729-23B2F5C01534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D5AA609-48B6-48E7-901F-4E149CDF9506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{2A19D64C-E665-4C5D-A1E9-A47E73BD3DB6}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{0DF69030-C37F-417B-84B2-BCD0EE4461F3}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2813" uniqueCount="1150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3035" uniqueCount="1150">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -3837,7 +3837,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D444407B-AEB7-4F20-AF58-B41552785B9E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28A1A3D8-1328-421D-9822-FEBA3267D61F}">
   <dimension ref="B3:S346"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12806,19 +12806,22 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5370EE85-A169-4E28-9D64-DFFDD015BA1E}">
-  <dimension ref="B3:L85"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9BB56C5-1002-496E-AB15-461C7CDC1A41}">
+  <dimension ref="B3:S112"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>0</v>
       </c>
       <c r="K3" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>1</v>
       </c>
@@ -12846,8 +12849,23 @@
       <c r="L4" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O4" t="s">
+        <v>316</v>
+      </c>
+      <c r="P4" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>318</v>
+      </c>
+      <c r="R4" t="s">
+        <v>319</v>
+      </c>
+      <c r="S4" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>8</v>
       </c>
@@ -12875,8 +12893,20 @@
       <c r="L5" t="s">
         <v>1069</v>
       </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O5" t="s">
+        <v>1023</v>
+      </c>
+      <c r="P5" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q5">
+        <v>117.16285659427568</v>
+      </c>
+      <c r="R5">
+        <v>30.541789021480241</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>8</v>
       </c>
@@ -12904,8 +12934,20 @@
       <c r="L6" t="s">
         <v>1070</v>
       </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O6" t="s">
+        <v>889</v>
+      </c>
+      <c r="P6" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q6">
+        <v>122.83437119448858</v>
+      </c>
+      <c r="R6">
+        <v>40.868138669862603</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>8</v>
       </c>
@@ -12933,8 +12975,20 @@
       <c r="L7" t="s">
         <v>1071</v>
       </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O7" t="s">
+        <v>903</v>
+      </c>
+      <c r="P7" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q7">
+        <v>105.84402816012648</v>
+      </c>
+      <c r="R7">
+        <v>26.221368237014666</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>8</v>
       </c>
@@ -12962,8 +13016,20 @@
       <c r="L8" t="s">
         <v>1072</v>
       </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O8" t="s">
+        <v>966</v>
+      </c>
+      <c r="P8" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q8">
+        <v>94.394264590364685</v>
+      </c>
+      <c r="R8">
+        <v>29.38813941656521</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>8</v>
       </c>
@@ -12991,8 +13057,20 @@
       <c r="L9" t="s">
         <v>1073</v>
       </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O9" t="s">
+        <v>972</v>
+      </c>
+      <c r="P9" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q9">
+        <v>113.06717626492392</v>
+      </c>
+      <c r="R9">
+        <v>40.397847664634988</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>8</v>
       </c>
@@ -13020,8 +13098,20 @@
       <c r="L10" t="s">
         <v>1074</v>
       </c>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O10" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P10" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q10">
+        <v>116.50611692326709</v>
+      </c>
+      <c r="R10">
+        <v>44.246247941994682</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -13049,8 +13139,20 @@
       <c r="L11" t="s">
         <v>1075</v>
       </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O11" t="s">
+        <v>1008</v>
+      </c>
+      <c r="P11" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q11">
+        <v>121.76680182666465</v>
+      </c>
+      <c r="R11">
+        <v>44.389603786504537</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>8</v>
       </c>
@@ -13078,8 +13180,20 @@
       <c r="L12" t="s">
         <v>1076</v>
       </c>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O12" t="s">
+        <v>941</v>
+      </c>
+      <c r="P12" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12">
+        <v>89.125609778782589</v>
+      </c>
+      <c r="R12">
+        <v>44.662494243085682</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>8</v>
       </c>
@@ -13107,8 +13221,20 @@
       <c r="L13" t="s">
         <v>1077</v>
       </c>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O13" t="s">
+        <v>952</v>
+      </c>
+      <c r="P13" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13">
+        <v>129.29586485345914</v>
+      </c>
+      <c r="R13">
+        <v>45.915538638519081</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>8</v>
       </c>
@@ -13136,8 +13262,20 @@
       <c r="L14" t="s">
         <v>1078</v>
       </c>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O14" t="s">
+        <v>901</v>
+      </c>
+      <c r="P14" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14">
+        <v>119.99010027882396</v>
+      </c>
+      <c r="R14">
+        <v>31.662906849198933</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>8</v>
       </c>
@@ -13165,8 +13303,20 @@
       <c r="L15" t="s">
         <v>1079</v>
       </c>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O15" t="s">
+        <v>918</v>
+      </c>
+      <c r="P15" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15">
+        <v>106.81312048139536</v>
+      </c>
+      <c r="R15">
+        <v>29.109833634960875</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>8</v>
       </c>
@@ -13194,8 +13344,20 @@
       <c r="L16" t="s">
         <v>1080</v>
       </c>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O16" t="s">
+        <v>920</v>
+      </c>
+      <c r="P16" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16">
+        <v>100.17412686401951</v>
+      </c>
+      <c r="R16">
+        <v>26.273636840355469</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
         <v>8</v>
       </c>
@@ -13223,8 +13385,20 @@
       <c r="L17" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O17" t="s">
+        <v>947</v>
+      </c>
+      <c r="P17" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17">
+        <v>108.39726207235805</v>
+      </c>
+      <c r="R17">
+        <v>21.59100156057184</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
         <v>8</v>
       </c>
@@ -13252,8 +13426,20 @@
       <c r="L18" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O18" t="s">
+        <v>962</v>
+      </c>
+      <c r="P18" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18">
+        <v>116.44818580639097</v>
+      </c>
+      <c r="R18">
+        <v>27.861313459403004</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
         <v>8</v>
       </c>
@@ -13281,8 +13467,20 @@
       <c r="L19" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O19" t="s">
+        <v>913</v>
+      </c>
+      <c r="P19" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19">
+        <v>119.94044244059836</v>
+      </c>
+      <c r="R19">
+        <v>30.39747603309122</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
         <v>8</v>
       </c>
@@ -13310,8 +13508,20 @@
       <c r="L20" t="s">
         <v>1084</v>
       </c>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O20" t="s">
+        <v>898</v>
+      </c>
+      <c r="P20" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20">
+        <v>126.51287898462628</v>
+      </c>
+      <c r="R20">
+        <v>45.572048615686725</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
         <v>8</v>
       </c>
@@ -13339,8 +13549,20 @@
       <c r="L21" t="s">
         <v>1085</v>
       </c>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O21" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P21" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21">
+        <v>110.95746517999513</v>
+      </c>
+      <c r="R21">
+        <v>35.545856255419906</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
         <v>8</v>
       </c>
@@ -13368,8 +13590,20 @@
       <c r="L22" t="s">
         <v>1086</v>
       </c>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O22" t="s">
+        <v>969</v>
+      </c>
+      <c r="P22" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22">
+        <v>111.43887067246216</v>
+      </c>
+      <c r="R22">
+        <v>40.438713867939562</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
         <v>8</v>
       </c>
@@ -13397,8 +13631,20 @@
       <c r="L23" t="s">
         <v>1087</v>
       </c>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O23" t="s">
+        <v>935</v>
+      </c>
+      <c r="P23" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23">
+        <v>101.53404466047556</v>
+      </c>
+      <c r="R23">
+        <v>25.949149871495983</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
         <v>8</v>
       </c>
@@ -13426,8 +13672,20 @@
       <c r="L24" t="s">
         <v>1088</v>
       </c>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O24" t="s">
+        <v>955</v>
+      </c>
+      <c r="P24" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24">
+        <v>112.9086448118706</v>
+      </c>
+      <c r="R24">
+        <v>30.335215729827794</v>
+      </c>
+    </row>
+    <row r="25" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
         <v>8</v>
       </c>
@@ -13455,8 +13713,20 @@
       <c r="L25" t="s">
         <v>1089</v>
       </c>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O25" t="s">
+        <v>925</v>
+      </c>
+      <c r="P25" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q25">
+        <v>83.023864223637872</v>
+      </c>
+      <c r="R25">
+        <v>41.824872154149837</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
         <v>8</v>
       </c>
@@ -13484,8 +13754,20 @@
       <c r="L26" t="s">
         <v>1090</v>
       </c>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O26" t="s">
+        <v>1002</v>
+      </c>
+      <c r="P26" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q26">
+        <v>123.3425242</v>
+      </c>
+      <c r="R26">
+        <v>41.379437087613979</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
         <v>8</v>
       </c>
@@ -13513,8 +13795,20 @@
       <c r="L27" t="s">
         <v>1091</v>
       </c>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O27" t="s">
+        <v>911</v>
+      </c>
+      <c r="P27" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q27">
+        <v>118.31649290214118</v>
+      </c>
+      <c r="R27">
+        <v>35.262325294510362</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
         <v>8</v>
       </c>
@@ -13542,8 +13836,20 @@
       <c r="L28" t="s">
         <v>1092</v>
       </c>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O28" t="s">
+        <v>937</v>
+      </c>
+      <c r="P28" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q28">
+        <v>109.63823599342832</v>
+      </c>
+      <c r="R28">
+        <v>24.523614463395774</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
         <v>8</v>
       </c>
@@ -13571,8 +13877,20 @@
       <c r="L29" t="s">
         <v>1093</v>
       </c>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O29" t="s">
+        <v>960</v>
+      </c>
+      <c r="P29" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29">
+        <v>114.19413545007455</v>
+      </c>
+      <c r="R29">
+        <v>33.610023416155371</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
         <v>8</v>
       </c>
@@ -13600,8 +13918,20 @@
       <c r="L30" t="s">
         <v>1094</v>
       </c>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O30" t="s">
+        <v>915</v>
+      </c>
+      <c r="P30" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q30">
+        <v>101.3712489125756</v>
+      </c>
+      <c r="R30">
+        <v>23.28453233552661</v>
+      </c>
+    </row>
+    <row r="31" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
         <v>8</v>
       </c>
@@ -13629,8 +13959,20 @@
       <c r="L31" t="s">
         <v>1095</v>
       </c>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O31" t="s">
+        <v>964</v>
+      </c>
+      <c r="P31" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q31">
+        <v>104.49151412864175</v>
+      </c>
+      <c r="R31">
+        <v>31.276515820874611</v>
+      </c>
+    </row>
+    <row r="32" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
         <v>8</v>
       </c>
@@ -13658,8 +14000,20 @@
       <c r="L32" t="s">
         <v>1096</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O32" t="s">
+        <v>980</v>
+      </c>
+      <c r="P32" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q32">
+        <v>118.64319586731661</v>
+      </c>
+      <c r="R32">
+        <v>31.947356949874443</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
         <v>8</v>
       </c>
@@ -13687,8 +14041,20 @@
       <c r="L33" t="s">
         <v>1097</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O33" t="s">
+        <v>1000</v>
+      </c>
+      <c r="P33" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q33">
+        <v>120.56203375515928</v>
+      </c>
+      <c r="R33">
+        <v>31.958081332582108</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
         <v>8</v>
       </c>
@@ -13716,8 +14082,20 @@
       <c r="L34" t="s">
         <v>1098</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O34" t="s">
+        <v>987</v>
+      </c>
+      <c r="P34" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q34">
+        <v>119.58662685561389</v>
+      </c>
+      <c r="R34">
+        <v>26.918649616323851</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
         <v>8</v>
       </c>
@@ -13745,8 +14123,20 @@
       <c r="L35" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O35" t="s">
+        <v>944</v>
+      </c>
+      <c r="P35" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q35">
+        <v>118.79159561630691</v>
+      </c>
+      <c r="R35">
+        <v>25.317124521019188</v>
+      </c>
+    </row>
+    <row r="36" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
         <v>8</v>
       </c>
@@ -13774,8 +14164,20 @@
       <c r="L36" t="s">
         <v>1100</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O36" t="s">
+        <v>974</v>
+      </c>
+      <c r="P36" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q36">
+        <v>100.46890056048989</v>
+      </c>
+      <c r="R36">
+        <v>36.11455069014589</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
         <v>8</v>
       </c>
@@ -13803,8 +14205,20 @@
       <c r="L37" t="s">
         <v>1101</v>
       </c>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O37" t="s">
+        <v>990</v>
+      </c>
+      <c r="P37" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q37">
+        <v>119.22561508125128</v>
+      </c>
+      <c r="R37">
+        <v>35.245296493701389</v>
+      </c>
+    </row>
+    <row r="38" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
         <v>8</v>
       </c>
@@ -13832,8 +14246,20 @@
       <c r="L38" t="s">
         <v>1102</v>
       </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O38" t="s">
+        <v>895</v>
+      </c>
+      <c r="P38" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q38">
+        <v>116.7357799710711</v>
+      </c>
+      <c r="R38">
+        <v>40.236864014905137</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
         <v>8</v>
       </c>
@@ -13861,8 +14287,20 @@
       <c r="L39" t="s">
         <v>1103</v>
       </c>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O39" t="s">
+        <v>922</v>
+      </c>
+      <c r="P39" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q39">
+        <v>120.00593799650504</v>
+      </c>
+      <c r="R39">
+        <v>40.18006242786187</v>
+      </c>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
         <v>8</v>
       </c>
@@ -13890,8 +14328,20 @@
       <c r="L40" t="s">
         <v>1104</v>
       </c>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O40" t="s">
+        <v>879</v>
+      </c>
+      <c r="P40" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q40">
+        <v>121.40711256286262</v>
+      </c>
+      <c r="R40">
+        <v>31.383619492955937</v>
+      </c>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
         <v>8</v>
       </c>
@@ -13919,8 +14369,20 @@
       <c r="L41" t="s">
         <v>1105</v>
       </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O41" t="s">
+        <v>977</v>
+      </c>
+      <c r="P41" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q41">
+        <v>113.57943301820916</v>
+      </c>
+      <c r="R41">
+        <v>24.615206775182561</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
         <v>8</v>
       </c>
@@ -13948,8 +14410,20 @@
       <c r="L42" t="s">
         <v>1106</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O42" t="s">
+        <v>883</v>
+      </c>
+      <c r="P42" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q42">
+        <v>114.5371075181218</v>
+      </c>
+      <c r="R42">
+        <v>38.244620822618266</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
         <v>8</v>
       </c>
@@ -13977,8 +14451,20 @@
       <c r="L43" t="s">
         <v>1107</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O43" t="s">
+        <v>1010</v>
+      </c>
+      <c r="P43" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q43">
+        <v>106.86915979066704</v>
+      </c>
+      <c r="R43">
+        <v>38.77999809379083</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
         <v>8</v>
       </c>
@@ -14006,8 +14492,20 @@
       <c r="L44" t="s">
         <v>1108</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O44" t="s">
+        <v>1004</v>
+      </c>
+      <c r="P44" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q44">
+        <v>118.56121832659292</v>
+      </c>
+      <c r="R44">
+        <v>39.698020093894968</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
         <v>8</v>
       </c>
@@ -14035,8 +14533,20 @@
       <c r="L45" t="s">
         <v>1109</v>
       </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O45" t="s">
+        <v>886</v>
+      </c>
+      <c r="P45" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45">
+        <v>117.4574504203509</v>
+      </c>
+      <c r="R45">
+        <v>38.961325621707822</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
         <v>8</v>
       </c>
@@ -14064,8 +14574,20 @@
       <c r="L46" t="s">
         <v>1110</v>
       </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O46" t="s">
+        <v>1021</v>
+      </c>
+      <c r="P46" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q46">
+        <v>117.9784677</v>
+      </c>
+      <c r="R46">
+        <v>31.125491877373417</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
         <v>8</v>
       </c>
@@ -14093,8 +14615,20 @@
       <c r="L47" t="s">
         <v>1111</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O47" t="s">
+        <v>1017</v>
+      </c>
+      <c r="P47" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47">
+        <v>117.36212706425869</v>
+      </c>
+      <c r="R47">
+        <v>34.113938755991278</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
         <v>8</v>
       </c>
@@ -14122,8 +14656,20 @@
       <c r="L48" t="s">
         <v>1112</v>
       </c>
-    </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O48" t="s">
+        <v>1019</v>
+      </c>
+      <c r="P48" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q48">
+        <v>113.94414451251799</v>
+      </c>
+      <c r="R48">
+        <v>36.644682729096289</v>
+      </c>
+    </row>
+    <row r="49" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
         <v>8</v>
       </c>
@@ -14151,8 +14697,20 @@
       <c r="L49" t="s">
         <v>1113</v>
       </c>
-    </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O49" t="s">
+        <v>892</v>
+      </c>
+      <c r="P49" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q49">
+        <v>114.58425776150936</v>
+      </c>
+      <c r="R49">
+        <v>30.505797154571937</v>
+      </c>
+    </row>
+    <row r="50" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
         <v>8</v>
       </c>
@@ -14180,8 +14738,20 @@
       <c r="L50" t="s">
         <v>1114</v>
       </c>
-    </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O50" t="s">
+        <v>928</v>
+      </c>
+      <c r="P50" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q50">
+        <v>104.68103641750832</v>
+      </c>
+      <c r="R50">
+        <v>36.819288557874472</v>
+      </c>
+    </row>
+    <row r="51" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
         <v>8</v>
       </c>
@@ -14209,8 +14779,20 @@
       <c r="L51" t="s">
         <v>1115</v>
       </c>
-    </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O51" t="s">
+        <v>998</v>
+      </c>
+      <c r="P51" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q51">
+        <v>110.9981566105884</v>
+      </c>
+      <c r="R51">
+        <v>30.81332652472457</v>
+      </c>
+    </row>
+    <row r="52" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
         <v>8</v>
       </c>
@@ -14238,8 +14820,20 @@
       <c r="L52" t="s">
         <v>1116</v>
       </c>
-    </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O52" t="s">
+        <v>984</v>
+      </c>
+      <c r="P52" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q52">
+        <v>111.50716511085272</v>
+      </c>
+      <c r="R52">
+        <v>35.724077277553754</v>
+      </c>
+    </row>
+    <row r="53" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
         <v>8</v>
       </c>
@@ -14267,8 +14861,20 @@
       <c r="L53" t="s">
         <v>1117</v>
       </c>
-    </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O53" t="s">
+        <v>939</v>
+      </c>
+      <c r="P53" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q53">
+        <v>102.86853612866496</v>
+      </c>
+      <c r="R53">
+        <v>28.048019479331803</v>
+      </c>
+    </row>
+    <row r="54" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
         <v>8</v>
       </c>
@@ -14296,8 +14902,20 @@
       <c r="L54" t="s">
         <v>1118</v>
       </c>
-    </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O54" t="s">
+        <v>908</v>
+      </c>
+      <c r="P54" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q54">
+        <v>119.73372948242414</v>
+      </c>
+      <c r="R54">
+        <v>49.324111574578367</v>
+      </c>
+    </row>
+    <row r="55" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
         <v>8</v>
       </c>
@@ -14325,8 +14943,20 @@
       <c r="L55" t="s">
         <v>1119</v>
       </c>
-    </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O55" t="s">
+        <v>992</v>
+      </c>
+      <c r="P55" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q55">
+        <v>119.0665272474164</v>
+      </c>
+      <c r="R55">
+        <v>39.32716160609354</v>
+      </c>
+    </row>
+    <row r="56" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
         <v>8</v>
       </c>
@@ -14354,8 +14984,20 @@
       <c r="L56" t="s">
         <v>1120</v>
       </c>
-    </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O56" t="s">
+        <v>933</v>
+      </c>
+      <c r="P56" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q56">
+        <v>111.91271228052884</v>
+      </c>
+      <c r="R56">
+        <v>21.989331758033583</v>
+      </c>
+    </row>
+    <row r="57" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
         <v>8</v>
       </c>
@@ -14383,8 +15025,20 @@
       <c r="L57" t="s">
         <v>1121</v>
       </c>
-    </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O57" t="s">
+        <v>1012</v>
+      </c>
+      <c r="P57" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q57">
+        <v>119.2469346898263</v>
+      </c>
+      <c r="R57">
+        <v>32.19401460504848</v>
+      </c>
+    </row>
+    <row r="58" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
         <v>8</v>
       </c>
@@ -14412,8 +15066,20 @@
       <c r="L58" t="s">
         <v>1122</v>
       </c>
-    </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O58" t="s">
+        <v>982</v>
+      </c>
+      <c r="P58" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q58">
+        <v>119.72158919912754</v>
+      </c>
+      <c r="R58">
+        <v>31.356509805163871</v>
+      </c>
+    </row>
+    <row r="59" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
         <v>8</v>
       </c>
@@ -14441,8 +15107,20 @@
       <c r="L59" t="s">
         <v>1123</v>
       </c>
-    </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O59" t="s">
+        <v>957</v>
+      </c>
+      <c r="P59" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q59">
+        <v>113.36221861482908</v>
+      </c>
+      <c r="R59">
+        <v>34.173741866473989</v>
+      </c>
+    </row>
+    <row r="60" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B60" t="s">
         <v>8</v>
       </c>
@@ -14470,8 +15148,20 @@
       <c r="L60" t="s">
         <v>1124</v>
       </c>
-    </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O60" t="s">
+        <v>906</v>
+      </c>
+      <c r="P60" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q60">
+        <v>112.27308469812009</v>
+      </c>
+      <c r="R60">
+        <v>28.504248372308155</v>
+      </c>
+    </row>
+    <row r="61" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B61" t="s">
         <v>8</v>
       </c>
@@ -14499,8 +15189,20 @@
       <c r="L61" t="s">
         <v>1125</v>
       </c>
-    </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O61" t="s">
+        <v>995</v>
+      </c>
+      <c r="P61" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q61">
+        <v>96.526106304860278</v>
+      </c>
+      <c r="R61">
+        <v>40.596974164272986</v>
+      </c>
+    </row>
+    <row r="62" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B62" t="s">
         <v>8</v>
       </c>
@@ -14528,8 +15230,20 @@
       <c r="L62" t="s">
         <v>1126</v>
       </c>
-    </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O62" t="s">
+        <v>931</v>
+      </c>
+      <c r="P62" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q62">
+        <v>107.61780765954406</v>
+      </c>
+      <c r="R62">
+        <v>23.298380367924931</v>
+      </c>
+    </row>
+    <row r="63" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B63" t="s">
         <v>8</v>
       </c>
@@ -14557,8 +15271,20 @@
       <c r="L63" t="s">
         <v>1127</v>
       </c>
-    </row>
-    <row r="64" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O63" t="s">
+        <v>949</v>
+      </c>
+      <c r="P63" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q63">
+        <v>117.40770327633828</v>
+      </c>
+      <c r="R63">
+        <v>37.191964309360991</v>
+      </c>
+    </row>
+    <row r="64" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B64" t="s">
         <v>8</v>
       </c>
@@ -14586,8 +15312,20 @@
       <c r="L64" t="s">
         <v>1128</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O64" t="s">
+        <v>916</v>
+      </c>
+      <c r="P64" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q64">
+        <v>108.6708333</v>
+      </c>
+      <c r="R64">
+        <v>20.826111109999999</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B65" t="s">
         <v>8</v>
       </c>
@@ -14615,8 +15353,20 @@
       <c r="L65" t="s">
         <v>1129</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O65" t="s">
+        <v>923</v>
+      </c>
+      <c r="P65" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q65">
+        <v>119.9233333</v>
+      </c>
+      <c r="R65">
+        <v>38.813333329999999</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B66" t="s">
         <v>8</v>
       </c>
@@ -14644,8 +15394,20 @@
       <c r="L66" t="s">
         <v>1130</v>
       </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O66" t="s">
+        <v>993</v>
+      </c>
+      <c r="P66" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q66">
+        <v>119.9205556</v>
+      </c>
+      <c r="R66">
+        <v>38.813333329999999</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B67" t="s">
         <v>8</v>
       </c>
@@ -14673,8 +15435,20 @@
       <c r="L67" t="s">
         <v>1131</v>
       </c>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O67" t="s">
+        <v>988</v>
+      </c>
+      <c r="P67" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q67">
+        <v>124.155</v>
+      </c>
+      <c r="R67">
+        <v>28.272777779999998</v>
+      </c>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
         <v>8</v>
       </c>
@@ -14702,8 +15476,20 @@
       <c r="L68" t="s">
         <v>1132</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O68" t="s">
+        <v>1025</v>
+      </c>
+      <c r="P68" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q68">
+        <v>116.42388889999999</v>
+      </c>
+      <c r="R68">
+        <v>39.904166670000002</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
         <v>8</v>
       </c>
@@ -14731,8 +15517,20 @@
       <c r="L69" t="s">
         <v>1133</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O69" t="s">
+        <v>945</v>
+      </c>
+      <c r="P69" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q69">
+        <v>115.6761111</v>
+      </c>
+      <c r="R69">
+        <v>21.00444444</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
         <v>8</v>
       </c>
@@ -14760,8 +15558,20 @@
       <c r="L70" t="s">
         <v>1134</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O70" t="s">
+        <v>978</v>
+      </c>
+      <c r="P70" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q70">
+        <v>115.6733333</v>
+      </c>
+      <c r="R70">
+        <v>21.00444444</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B71" t="s">
         <v>8</v>
       </c>
@@ -14789,8 +15599,20 @@
       <c r="L71" t="s">
         <v>1135</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O71" t="s">
+        <v>1027</v>
+      </c>
+      <c r="P71" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q71">
+        <v>108.3152778</v>
+      </c>
+      <c r="R71">
+        <v>17.661944439999999</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B72" t="s">
         <v>8</v>
       </c>
@@ -14818,8 +15640,20 @@
       <c r="L72" t="s">
         <v>1136</v>
       </c>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O72" t="s">
+        <v>896</v>
+      </c>
+      <c r="P72" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q72">
+        <v>116.545</v>
+      </c>
+      <c r="R72">
+        <v>40.166944440000002</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B73" t="s">
         <v>8</v>
       </c>
@@ -14847,8 +15681,20 @@
       <c r="L73" t="s">
         <v>1137</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O73" t="s">
+        <v>1029</v>
+      </c>
+      <c r="P73" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q73">
+        <v>116.5422222</v>
+      </c>
+      <c r="R73">
+        <v>40.166944440000002</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B74" t="s">
         <v>8</v>
       </c>
@@ -14876,8 +15722,20 @@
       <c r="L74" t="s">
         <v>1138</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O74" t="s">
+        <v>1015</v>
+      </c>
+      <c r="P74" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q74">
+        <v>113.1891667</v>
+      </c>
+      <c r="R74">
+        <v>43.663888890000003</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B75" t="s">
         <v>8</v>
       </c>
@@ -14905,8 +15763,20 @@
       <c r="L75" t="s">
         <v>1139</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O75" t="s">
+        <v>893</v>
+      </c>
+      <c r="P75" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q75">
+        <v>112.19499999999999</v>
+      </c>
+      <c r="R75">
+        <v>30.032222220000001</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B76" t="s">
         <v>8</v>
       </c>
@@ -14934,8 +15804,20 @@
       <c r="L76" t="s">
         <v>1140</v>
       </c>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O76" t="s">
+        <v>996</v>
+      </c>
+      <c r="P76" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q76">
+        <v>96.617500000000007</v>
+      </c>
+      <c r="R76">
+        <v>39.486111110000003</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B77" t="s">
         <v>8</v>
       </c>
@@ -14963,8 +15845,20 @@
       <c r="L77" t="s">
         <v>1141</v>
       </c>
-    </row>
-    <row r="78" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O77" t="s">
+        <v>975</v>
+      </c>
+      <c r="P77" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q77">
+        <v>98.700833329999995</v>
+      </c>
+      <c r="R77">
+        <v>39.821111109999997</v>
+      </c>
+    </row>
+    <row r="78" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B78" t="s">
         <v>8</v>
       </c>
@@ -14992,8 +15886,20 @@
       <c r="L78" t="s">
         <v>1142</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O78" t="s">
+        <v>1031</v>
+      </c>
+      <c r="P78" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q78">
+        <v>87.832222220000006</v>
+      </c>
+      <c r="R78">
+        <v>45.170555559999997</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B79" t="s">
         <v>8</v>
       </c>
@@ -15021,8 +15927,20 @@
       <c r="L79" t="s">
         <v>1143</v>
       </c>
-    </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O79" t="s">
+        <v>1033</v>
+      </c>
+      <c r="P79" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q79">
+        <v>84.716944440000006</v>
+      </c>
+      <c r="R79">
+        <v>44.904166670000002</v>
+      </c>
+    </row>
+    <row r="80" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B80" t="s">
         <v>8</v>
       </c>
@@ -15050,8 +15968,20 @@
       <c r="L80" t="s">
         <v>1144</v>
       </c>
-    </row>
-    <row r="81" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O80" t="s">
+        <v>1035</v>
+      </c>
+      <c r="P80" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q80">
+        <v>122.65527779999999</v>
+      </c>
+      <c r="R80">
+        <v>41.606111110000001</v>
+      </c>
+    </row>
+    <row r="81" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B81" t="s">
         <v>8</v>
       </c>
@@ -15079,8 +16009,20 @@
       <c r="L81" t="s">
         <v>1145</v>
       </c>
-    </row>
-    <row r="82" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O81" t="s">
+        <v>890</v>
+      </c>
+      <c r="P81" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q81">
+        <v>122.6580556</v>
+      </c>
+      <c r="R81">
+        <v>41.606111110000001</v>
+      </c>
+    </row>
+    <row r="82" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B82" t="s">
         <v>8</v>
       </c>
@@ -15108,8 +16050,20 @@
       <c r="L82" t="s">
         <v>1146</v>
       </c>
-    </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O82" t="s">
+        <v>985</v>
+      </c>
+      <c r="P82" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q82">
+        <v>112.4075</v>
+      </c>
+      <c r="R82">
+        <v>32.833888889999997</v>
+      </c>
+    </row>
+    <row r="83" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B83" t="s">
         <v>8</v>
       </c>
@@ -15137,8 +16091,20 @@
       <c r="L83" t="s">
         <v>1147</v>
       </c>
-    </row>
-    <row r="84" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O83" t="s">
+        <v>958</v>
+      </c>
+      <c r="P83" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q83">
+        <v>113.02611109999999</v>
+      </c>
+      <c r="R83">
+        <v>32.664999999999999</v>
+      </c>
+    </row>
+    <row r="84" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B84" t="s">
         <v>8</v>
       </c>
@@ -15166,8 +16132,20 @@
       <c r="L84" t="s">
         <v>1148</v>
       </c>
-    </row>
-    <row r="85" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O84" t="s">
+        <v>929</v>
+      </c>
+      <c r="P84" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q84">
+        <v>108.1538889</v>
+      </c>
+      <c r="R84">
+        <v>37.165555560000001</v>
+      </c>
+    </row>
+    <row r="85" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B85" t="s">
         <v>8</v>
       </c>
@@ -15194,6 +16172,396 @@
       </c>
       <c r="L85" t="s">
         <v>1149</v>
+      </c>
+      <c r="O85" t="s">
+        <v>1037</v>
+      </c>
+      <c r="P85" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q85">
+        <v>108.1538889</v>
+      </c>
+      <c r="R85">
+        <v>37.165555560000001</v>
+      </c>
+    </row>
+    <row r="86" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="O86" t="s">
+        <v>967</v>
+      </c>
+      <c r="P86" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q86">
+        <v>93.294444440000007</v>
+      </c>
+      <c r="R86">
+        <v>37.544444439999999</v>
+      </c>
+    </row>
+    <row r="87" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="O87" t="s">
+        <v>1039</v>
+      </c>
+      <c r="P87" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q87">
+        <v>90.766388890000002</v>
+      </c>
+      <c r="R87">
+        <v>38.312222220000002</v>
+      </c>
+    </row>
+    <row r="88" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="O88" t="s">
+        <v>1041</v>
+      </c>
+      <c r="P88" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q88">
+        <v>107.25</v>
+      </c>
+      <c r="R88">
+        <v>29.710277779999998</v>
+      </c>
+    </row>
+    <row r="89" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="O89" t="s">
+        <v>904</v>
+      </c>
+      <c r="P89" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q89">
+        <v>107.2472222</v>
+      </c>
+      <c r="R89">
+        <v>29.710277779999998</v>
+      </c>
+    </row>
+    <row r="90" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="O90" t="s">
+        <v>909</v>
+      </c>
+      <c r="P90" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q90">
+        <v>123.8936111</v>
+      </c>
+      <c r="R90">
+        <v>43.647777779999998</v>
+      </c>
+    </row>
+    <row r="91" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="O91" t="s">
+        <v>1043</v>
+      </c>
+      <c r="P91" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q91">
+        <v>123.89638890000001</v>
+      </c>
+      <c r="R91">
+        <v>43.647777779999998</v>
+      </c>
+    </row>
+    <row r="92" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="O92" t="s">
+        <v>880</v>
+      </c>
+      <c r="P92" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q92">
+        <v>120.13083330000001</v>
+      </c>
+      <c r="R92">
+        <v>32.668888889999998</v>
+      </c>
+    </row>
+    <row r="93" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="O93" t="s">
+        <v>1045</v>
+      </c>
+      <c r="P93" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q93">
+        <v>120.13083330000001</v>
+      </c>
+      <c r="R93">
+        <v>32.668888889999998</v>
+      </c>
+    </row>
+    <row r="94" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="O94" t="s">
+        <v>1047</v>
+      </c>
+      <c r="P94" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q94">
+        <v>77.218888890000002</v>
+      </c>
+      <c r="R94">
+        <v>37.27416667</v>
+      </c>
+    </row>
+    <row r="95" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="O95" t="s">
+        <v>1049</v>
+      </c>
+      <c r="P95" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q95">
+        <v>76.347222220000006</v>
+      </c>
+      <c r="R95">
+        <v>37.375277779999998</v>
+      </c>
+    </row>
+    <row r="96" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="O96" t="s">
+        <v>1051</v>
+      </c>
+      <c r="P96" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q96">
+        <v>90.199444439999994</v>
+      </c>
+      <c r="R96">
+        <v>43.743055560000002</v>
+      </c>
+    </row>
+    <row r="97" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O97" t="s">
+        <v>1053</v>
+      </c>
+      <c r="P97" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q97">
+        <v>90.199444439999994</v>
+      </c>
+      <c r="R97">
+        <v>43.743055560000002</v>
+      </c>
+    </row>
+    <row r="98" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O98" t="s">
+        <v>926</v>
+      </c>
+      <c r="P98" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q98">
+        <v>86.873333329999994</v>
+      </c>
+      <c r="R98">
+        <v>42.135277780000003</v>
+      </c>
+    </row>
+    <row r="99" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O99" t="s">
+        <v>1055</v>
+      </c>
+      <c r="P99" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q99">
+        <v>86.876111109999997</v>
+      </c>
+      <c r="R99">
+        <v>42.135277780000003</v>
+      </c>
+    </row>
+    <row r="100" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O100" t="s">
+        <v>953</v>
+      </c>
+      <c r="P100" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q100">
+        <v>127.27083330000001</v>
+      </c>
+      <c r="R100">
+        <v>44.761666669999997</v>
+      </c>
+    </row>
+    <row r="101" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O101" t="s">
+        <v>899</v>
+      </c>
+      <c r="P101" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101">
+        <v>127.2680556</v>
+      </c>
+      <c r="R101">
+        <v>44.761666669999997</v>
+      </c>
+    </row>
+    <row r="102" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O102" t="s">
+        <v>970</v>
+      </c>
+      <c r="P102" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q102">
+        <v>110.07361109999999</v>
+      </c>
+      <c r="R102">
+        <v>39.380000000000003</v>
+      </c>
+    </row>
+    <row r="103" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O103" t="s">
+        <v>884</v>
+      </c>
+      <c r="P103" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q103">
+        <v>116.40722220000001</v>
+      </c>
+      <c r="R103">
+        <v>39.904166670000002</v>
+      </c>
+    </row>
+    <row r="104" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O104" t="s">
+        <v>1057</v>
+      </c>
+      <c r="P104" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q104">
+        <v>117.4216667</v>
+      </c>
+      <c r="R104">
+        <v>38.704166669999999</v>
+      </c>
+    </row>
+    <row r="105" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O105" t="s">
+        <v>1059</v>
+      </c>
+      <c r="P105" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q105">
+        <v>117.4244444</v>
+      </c>
+      <c r="R105">
+        <v>38.704166669999999</v>
+      </c>
+    </row>
+    <row r="106" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O106" t="s">
+        <v>1061</v>
+      </c>
+      <c r="P106" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q106">
+        <v>117.43</v>
+      </c>
+      <c r="R106">
+        <v>38.704166669999999</v>
+      </c>
+    </row>
+    <row r="107" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O107" t="s">
+        <v>1063</v>
+      </c>
+      <c r="P107" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q107">
+        <v>117.4327778</v>
+      </c>
+      <c r="R107">
+        <v>38.704166669999999</v>
+      </c>
+    </row>
+    <row r="108" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O108" t="s">
+        <v>1065</v>
+      </c>
+      <c r="P108" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q108">
+        <v>117.4355556</v>
+      </c>
+      <c r="R108">
+        <v>38.704166669999999</v>
+      </c>
+    </row>
+    <row r="109" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O109" t="s">
+        <v>887</v>
+      </c>
+      <c r="P109" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q109">
+        <v>117.4383333</v>
+      </c>
+      <c r="R109">
+        <v>38.704166669999999</v>
+      </c>
+    </row>
+    <row r="110" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O110" t="s">
+        <v>950</v>
+      </c>
+      <c r="P110" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q110">
+        <v>117.4188889</v>
+      </c>
+      <c r="R110">
+        <v>38.704166669999999</v>
+      </c>
+    </row>
+    <row r="111" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O111" t="s">
+        <v>1067</v>
+      </c>
+      <c r="P111" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q111">
+        <v>117.4272222</v>
+      </c>
+      <c r="R111">
+        <v>38.704166669999999</v>
+      </c>
+    </row>
+    <row r="112" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O112" t="s">
+        <v>942</v>
+      </c>
+      <c r="P112" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q112">
+        <v>88.431666669999998</v>
+      </c>
+      <c r="R112">
+        <v>44.459722220000003</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_CHN_grids_kan60/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_CHN_grids_kan60/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D5AA609-48B6-48E7-901F-4E149CDF9506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{093760B7-33BC-42F4-8933-92C6B18C35F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{0DF69030-C37F-417B-84B2-BCD0EE4461F3}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{C9CF983E-086B-41CB-A591-3D63A04D7001}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3837,7 +3837,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28A1A3D8-1328-421D-9822-FEBA3267D61F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1D89454-0DAF-4A65-AFBD-2D5C978B15B1}">
   <dimension ref="B3:S346"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12806,7 +12806,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9BB56C5-1002-496E-AB15-461C7CDC1A41}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2543361-7337-4EA5-807F-11B35D01448E}">
   <dimension ref="B3:S112"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHN_grids_kan60/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_CHN_grids_kan60/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{093760B7-33BC-42F4-8933-92C6B18C35F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5852ED1-2DD9-496A-AA53-1B97974F21AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{C9CF983E-086B-41CB-A591-3D63A04D7001}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="12772" activeTab="1" xr2:uid="{16974A4F-F6E1-451B-921B-8D9EF6F8D4FC}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3035" uniqueCount="1150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3035" uniqueCount="1151">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -984,7 +984,7 @@
     <t>grid link -42.0 km- way/1019608118-500;way/610573755-1000 (thermal x 0.7 N-1)</t>
   </si>
   <si>
-    <t>~commodity_geo</t>
+    <t>~commodity_geo:network=electricity</t>
   </si>
   <si>
     <t>commodity</t>
@@ -3487,6 +3487,9 @@
   </si>
   <si>
     <t>co2 pipeline -34 km- way/133523400-500 to ogci_10271.0</t>
+  </si>
+  <si>
+    <t>~commodity_geo:network=co2</t>
   </si>
 </sst>
 </file>
@@ -3837,7 +3840,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1D89454-0DAF-4A65-AFBD-2D5C978B15B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A3FFCC5-7926-4030-A07F-2DEFE4873FDE}">
   <dimension ref="B3:S346"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12806,7 +12809,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2543361-7337-4EA5-807F-11B35D01448E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FA6AAD5-F16B-40EB-928C-C975956CD8D9}">
   <dimension ref="B3:S112"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12818,7 +12821,7 @@
         <v>191</v>
       </c>
       <c r="O3" t="s">
-        <v>315</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.45">

--- a/VerveStacks_CHN_grids_kan60/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_CHN_grids_kan60/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5852ED1-2DD9-496A-AA53-1B97974F21AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C61886C1-9BD8-43AD-905E-DF51E48DE83F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="12772" activeTab="1" xr2:uid="{16974A4F-F6E1-451B-921B-8D9EF6F8D4FC}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12773" activeTab="1" xr2:uid="{21495D92-8928-4276-82B2-FB777FC8A778}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3840,7 +3840,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A3FFCC5-7926-4030-A07F-2DEFE4873FDE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D38CD5CE-5B9E-40D9-8071-195B313F9437}">
   <dimension ref="B3:S346"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12809,7 +12809,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FA6AAD5-F16B-40EB-928C-C975956CD8D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AEDDAC4-E291-4ECB-BC24-CA4809E1D33B}">
   <dimension ref="B3:S112"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
